--- a/data/trans_camb/P1002-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1002-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,91</t>
+          <t>0,23; 5,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,46</t>
+          <t>-0,09; 4,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 3,68</t>
+          <t>-0,71; 3,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 12,85</t>
+          <t>6,71; 12,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,11</t>
+          <t>3,29; 9,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,8</t>
+          <t>1,74; 6,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,16</t>
+          <t>4,28; 8,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,25</t>
+          <t>2,26; 5,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,65</t>
+          <t>1,21; 4,59</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 170,95</t>
+          <t>1,92; 163,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 162,88</t>
+          <t>-1,96; 168,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 132,86</t>
+          <t>-16,52; 124,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102,83; 330,08</t>
+          <t>102,53; 330,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,77; 230,14</t>
+          <t>49,12; 230,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,34; 172,51</t>
+          <t>24,9; 167,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,57; 210,07</t>
+          <t>78,03; 213,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,43; 165,54</t>
+          <t>44,44; 159,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,96; 118,9</t>
+          <t>20,13; 121,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,39</t>
+          <t>-0,31; 4,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,48</t>
+          <t>-3,4; 0,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 1,34</t>
+          <t>-3,74; 1,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,23</t>
+          <t>4,7; 10,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,06</t>
+          <t>0,54; 5,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,27</t>
+          <t>0,22; 5,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 6,39</t>
+          <t>2,82; 6,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,56</t>
+          <t>-0,59; 2,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,45</t>
+          <t>-1,85; 2,4</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 102,18</t>
+          <t>-5,82; 101,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,78; 11,7</t>
+          <t>-53,76; 11,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,45; 30,33</t>
+          <t>-61,37; 24,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50,2; 172,93</t>
+          <t>53,16; 168,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,43; 98,33</t>
+          <t>5,78; 97,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 86,92</t>
+          <t>2,59; 88,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,51; 118,21</t>
+          <t>40,56; 120,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 46,62</t>
+          <t>-8,08; 49,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 43,45</t>
+          <t>-24,62; 41,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,35</t>
+          <t>-3,44; 2,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,16</t>
+          <t>-4,16; 1,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 4,4</t>
+          <t>-1,68; 4,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 4,56</t>
+          <t>-2,56; 4,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 2,21</t>
+          <t>-4,24; 2,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -0,22</t>
+          <t>-9,44; 0,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,2</t>
+          <t>-2,09; 2,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,93</t>
+          <t>-3,3; 0,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 1,22</t>
+          <t>-4,26; 1,28</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,65; 46,4</t>
+          <t>-45,2; 43,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,84; 27,77</t>
+          <t>-53,26; 23,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 91,06</t>
+          <t>-21,81; 88,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 43,41</t>
+          <t>-18,91; 39,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,82; 21,45</t>
+          <t>-30,97; 21,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,35; -2,86</t>
+          <t>-68,34; -0,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 26,42</t>
+          <t>-20,45; 25,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 11,74</t>
+          <t>-31,55; 8,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 13,94</t>
+          <t>-41,93; 13,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,0</t>
+          <t>-0,48; 4,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,92</t>
+          <t>-0,68; 3,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,87</t>
+          <t>-2,0; 1,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,92</t>
+          <t>1,66; 7,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,39</t>
+          <t>-2,09; 3,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 4,67</t>
+          <t>-1,33; 4,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,82</t>
+          <t>1,14; 4,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,7</t>
+          <t>-0,85; 2,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,92</t>
+          <t>-0,65; 2,82</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 92,05</t>
+          <t>-8,06; 97,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 90,69</t>
+          <t>-11,4; 87,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,06; 43,71</t>
+          <t>-32,33; 46,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,7; 85,48</t>
+          <t>14,54; 93,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 43,31</t>
+          <t>-19,76; 41,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 58,05</t>
+          <t>-12,41; 59,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,95; 73,5</t>
+          <t>14,32; 74,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 40,11</t>
+          <t>-10,15; 39,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 45,05</t>
+          <t>-8,06; 42,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,86</t>
+          <t>0,39; 2,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,29</t>
+          <t>-0,9; 1,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,46</t>
+          <t>-1,23; 1,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,06</t>
+          <t>4,07; 7,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,63</t>
+          <t>0,83; 3,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,84</t>
+          <t>-0,57; 2,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,54</t>
+          <t>2,57; 4,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,06</t>
+          <t>0,27; 2,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,87</t>
+          <t>-0,3; 1,93</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,52; 61,43</t>
+          <t>7,03; 59,19</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 28,6</t>
+          <t>-16,25; 26,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 30,5</t>
+          <t>-21,92; 30,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44,25; 89,79</t>
+          <t>44,12; 91,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,2; 45,48</t>
+          <t>9,56; 46,76</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 35,68</t>
+          <t>-6,1; 37,33</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,21; 71,56</t>
+          <t>35,0; 71,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,46; 31,8</t>
+          <t>3,55; 32,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 28,85</t>
+          <t>-3,94; 29,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1002-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1002-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>4,42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,93</t>
+          <t>3,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,07</t>
+          <t>0,26; 4,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 4,68</t>
+          <t>-0,31; 4,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 3,8</t>
+          <t>-0,85; 3,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 12,97</t>
+          <t>6,24; 12,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 9,26</t>
+          <t>2,96; 8,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,63</t>
+          <t>2,22; 6,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 8,2</t>
+          <t>4,25; 8,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,99</t>
+          <t>2,31; 6,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,59</t>
+          <t>1,46; 4,61</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>66,32%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 163,12</t>
+          <t>3,46; 161,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 168,22</t>
+          <t>-7,41; 153,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 124,79</t>
+          <t>-17,66; 132,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102,53; 330,54</t>
+          <t>98,8; 303,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,12; 230,41</t>
+          <t>44,05; 212,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,9; 167,0</t>
+          <t>33,79; 169,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,03; 213,69</t>
+          <t>80,54; 223,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,44; 159,3</t>
+          <t>42,87; 161,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,13; 121,56</t>
+          <t>26,47; 121,35</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,96</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>1,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,42</t>
+          <t>-0,03; 4,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,48</t>
+          <t>-3,29; 0,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,17</t>
+          <t>-2,03; 2,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 10,13</t>
+          <t>4,55; 10,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,98</t>
+          <t>0,51; 5,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 5,23</t>
+          <t>0,4; 5,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,54</t>
+          <t>2,79; 6,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,69</t>
+          <t>-0,77; 2,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,4</t>
+          <t>-0,11; 3,07</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-18,34%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>25,08%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 101,63</t>
+          <t>-1,7; 99,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,76; 11,62</t>
+          <t>-52,1; 11,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 24,91</t>
+          <t>-32,16; 48,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53,16; 168,59</t>
+          <t>52,42; 174,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,78; 97,55</t>
+          <t>5,17; 94,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 88,72</t>
+          <t>2,9; 85,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,56; 120,16</t>
+          <t>38,96; 117,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 49,7</t>
+          <t>-10,52; 47,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 41,99</t>
+          <t>-0,62; 57,44</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,77</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-0,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 2,21</t>
+          <t>-3,39; 2,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 1,11</t>
+          <t>-3,99; 1,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 4,39</t>
+          <t>-1,5; 4,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,23</t>
+          <t>-3,31; 3,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 2,22</t>
+          <t>-4,21; 2,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 0,04</t>
+          <t>-4,06; 2,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,13</t>
+          <t>-2,18; 2,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,71</t>
+          <t>-3,24; 1,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,28</t>
+          <t>-2,26; 2,14</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-30,84%</t>
+          <t>-8,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-12,52%</t>
+          <t>-0,43%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,2; 43,92</t>
+          <t>-44,32; 40,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,26; 23,32</t>
+          <t>-51,96; 23,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 88,98</t>
+          <t>-21,52; 82,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 39,82</t>
+          <t>-23,03; 36,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 21,83</t>
+          <t>-30,26; 21,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,34; -0,19</t>
+          <t>-28,44; 21,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,45; 25,57</t>
+          <t>-20,13; 30,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,55; 8,63</t>
+          <t>-31,69; 13,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 13,71</t>
+          <t>-21,16; 25,23</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,15</t>
+          <t>-0,66; 3,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,83</t>
+          <t>-0,95; 3,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,96</t>
+          <t>-2,18; 1,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 7,37</t>
+          <t>1,73; 7,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 3,4</t>
+          <t>-2,28; 3,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,72</t>
+          <t>0,03; 4,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,88</t>
+          <t>1,13; 4,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,62</t>
+          <t>-0,63; 2,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,82</t>
+          <t>-0,22; 2,86</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0,76%</t>
+          <t>-4,45%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 97,71</t>
+          <t>-10,93; 87,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 87,08</t>
+          <t>-14,15; 82,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 46,99</t>
+          <t>-33,63; 42,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,54; 93,4</t>
+          <t>16,29; 91,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 41,24</t>
+          <t>-21,71; 38,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 59,54</t>
+          <t>0,27; 61,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,32; 74,24</t>
+          <t>13,32; 71,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 39,73</t>
+          <t>-7,98; 39,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 42,15</t>
+          <t>-2,4; 45,29</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,47</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,73</t>
+          <t>0,36; 2,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,22</t>
+          <t>-0,92; 1,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,43</t>
+          <t>-0,63; 1,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,18</t>
+          <t>3,87; 6,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,68</t>
+          <t>0,63; 3,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,98</t>
+          <t>1,04; 3,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,57</t>
+          <t>2,59; 4,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,1</t>
+          <t>0,3; 2,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,93</t>
+          <t>0,56; 2,31</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>7,03; 59,19</t>
+          <t>6,09; 58,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 26,26</t>
+          <t>-16,37; 26,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 30,37</t>
+          <t>-10,56; 36,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44,12; 91,04</t>
+          <t>40,8; 87,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,56; 46,76</t>
+          <t>6,9; 47,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 37,33</t>
+          <t>11,53; 44,8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,0; 71,26</t>
+          <t>35,23; 70,43</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3,55; 32,82</t>
+          <t>4,04; 32,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 29,72</t>
+          <t>7,7; 36,07</t>
         </is>
       </c>
     </row>
